--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ266"/>
+  <dimension ref="A1:AZ267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24866,10 +24866,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>54917729</v>
+        <v>136475971</v>
       </c>
       <c r="B208" t="n">
-        <v>57966</v>
+        <v>93435</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24877,48 +24877,40 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100048</v>
+        <v>5964</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Forsla kärr, Srm</t>
+          <t>SV Forsla kärr, Srm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>681764</v>
+        <v>681512</v>
       </c>
       <c r="R208" t="n">
-        <v>6562403</v>
+        <v>6562236</v>
       </c>
       <c r="S208" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -24942,22 +24934,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2015-08-23</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2015-08-23</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24966,50 +24948,51 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Anders Tranberg</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Anders Tranberg</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54917729</t>
+          <t>https://artportalen.se/Sighting/136475971</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>55904725</v>
+        <v>54917729</v>
       </c>
       <c r="B209" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -25031,17 +25014,17 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>österhaninge, forsla kärr w dalarövägen, Srm</t>
+          <t>Forsla kärr, Srm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>681632</v>
+        <v>681764</v>
       </c>
       <c r="R209" t="n">
-        <v>6562243</v>
+        <v>6562403</v>
       </c>
       <c r="S209" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -25065,27 +25048,22 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2015-11-21</t>
+          <t>2015-08-23</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2015-11-21</t>
+          <t>2015-08-23</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>W.- ut ( Barndomsminne...)</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -25100,79 +25078,76 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Anders Tranberg</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Anders Tranberg</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55904725</t>
+          <t>https://artportalen.se/Sighting/54917729</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>14178919</v>
+        <v>55904725</v>
       </c>
       <c r="B210" t="n">
-        <v>43219</v>
+        <v>57950</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>201028</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra delen, Srm</t>
+          <t>österhaninge, forsla kärr w dalarövägen, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>681771</v>
+        <v>681632</v>
       </c>
       <c r="R210" t="n">
-        <v>6562344</v>
+        <v>6562243</v>
       </c>
       <c r="S210" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -25196,12 +25171,27 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2009-07-18</t>
+          <t>2015-11-21</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2009-07-18</t>
+          <t>2015-11-21</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>W.- ut ( Barndomsminne...)</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -25216,58 +25206,54 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Karl-Erik Lidberg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Karl-Erik Lidberg</t>
-        </is>
-      </c>
-      <c r="AY210" t="inlineStr">
-        <is>
-          <t>Dagfjärilar i Södermanland</t>
-        </is>
-      </c>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14178919</t>
+          <t>https://artportalen.se/Sighting/55904725</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>14178920</v>
+        <v>14178919</v>
       </c>
       <c r="B211" t="n">
-        <v>43378</v>
+        <v>43219</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>201075</v>
+        <v>201028</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -25351,16 +25337,16 @@
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14178920</t>
+          <t>https://artportalen.se/Sighting/14178919</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>14176131</v>
+        <v>14178920</v>
       </c>
       <c r="B212" t="n">
-        <v>43285</v>
+        <v>43378</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25368,21 +25354,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>201143</v>
+        <v>201075</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ängsblåvinge</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Cyaniris semiargus</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -25436,12 +25422,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2009-06-24</t>
+          <t>2009-07-18</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2009-06-24</t>
+          <t>2009-07-18</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -25471,38 +25457,38 @@
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14176131</t>
+          <t>https://artportalen.se/Sighting/14178920</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>86387466</v>
+        <v>14176131</v>
       </c>
       <c r="B213" t="n">
-        <v>58790</v>
+        <v>43285</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>208245</v>
+        <v>201143</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ängsblåvinge</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Cyaniris semiargus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -25510,40 +25496,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr"/>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>vilande</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>österhaninge, forsla kärr w dalarövägen, Srm</t>
+          <t>Forsla kärr, södra delen, Srm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>681632</v>
+        <v>681771</v>
       </c>
       <c r="R213" t="n">
-        <v>6562243</v>
+        <v>6562344</v>
       </c>
       <c r="S213" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -25567,17 +25542,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
+          <t>2009-06-24</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>Våtmark. Myndig bjässe...( - Som von Linnés´ Nemesis, Buffon ? ).</t>
+          <t>2009-06-24</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -25586,34 +25556,37 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
-      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Karl-Erik Lidberg</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
-        </is>
-      </c>
-      <c r="AY213" t="inlineStr"/>
+          <t>Karl-Erik Lidberg</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>Dagfjärilar i Södermanland</t>
+        </is>
+      </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86387466</t>
+          <t>https://artportalen.se/Sighting/14176131</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>55904693</v>
+        <v>86387466</v>
       </c>
       <c r="B214" t="n">
-        <v>99026</v>
+        <v>58790</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25621,35 +25594,49 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>219788</v>
+        <v>208245</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>österhaninge, forsla kärr w dalarövägen, Srm</t>
@@ -25686,17 +25673,17 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2015-11-21</t>
+          <t>2020-06-20</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2015-11-21</t>
+          <t>2020-06-20</t>
         </is>
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>Öppet medelrikkärr; Åtm. 1. ( Slåtter har skett ! )</t>
+          <t>Våtmark. Myndig bjässe...( - Som von Linnés´ Nemesis, Buffon ? ).</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -25705,6 +25692,7 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
+      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -25722,13 +25710,13 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55904693</t>
+          <t>https://artportalen.se/Sighting/86387466</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>66416552</v>
+        <v>55904693</v>
       </c>
       <c r="B215" t="n">
         <v>99026</v>
@@ -25756,24 +25744,31 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren - yta 05, Srm</t>
+          <t>österhaninge, forsla kärr w dalarövägen, Srm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>681680</v>
+        <v>681632</v>
       </c>
       <c r="R215" t="n">
-        <v>6562385</v>
+        <v>6562243</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -25797,12 +25792,17 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2015-11-21</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2015-11-21</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>Öppet medelrikkärr; Åtm. 1. ( Slåtter har skett ! )</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -25813,33 +25813,28 @@
       </c>
       <c r="AG215" t="b">
         <v>0</v>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>medelrikkärr</t>
-        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416552</t>
+          <t>https://artportalen.se/Sighting/55904693</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>66416553</v>
+        <v>66416552</v>
       </c>
       <c r="B216" t="n">
         <v>99026</v>
@@ -25869,19 +25864,19 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren - yta 09, Srm</t>
+          <t>Forsla kärr, södra myren - yta 05, Srm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>681752</v>
+        <v>681680</v>
       </c>
       <c r="R216" t="n">
-        <v>6562360</v>
+        <v>6562385</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25944,13 +25939,13 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416553</t>
+          <t>https://artportalen.se/Sighting/66416552</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>66416554</v>
+        <v>66416553</v>
       </c>
       <c r="B217" t="n">
         <v>99026</v>
@@ -25980,19 +25975,19 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren - yta 10, Srm</t>
+          <t>Forsla kärr, södra myren - yta 09, Srm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>681778</v>
+        <v>681752</v>
       </c>
       <c r="R217" t="n">
-        <v>6562364</v>
+        <v>6562360</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -26055,16 +26050,16 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416554</t>
+          <t>https://artportalen.se/Sighting/66416553</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>104596865</v>
+        <v>66416554</v>
       </c>
       <c r="B218" t="n">
-        <v>106244</v>
+        <v>99026</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -26072,42 +26067,38 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221144</v>
+        <v>219788</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>V Forsla kärr, Srm</t>
+          <t>Forsla kärr, södra myren - yta 10, Srm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>681619</v>
+        <v>681778</v>
       </c>
       <c r="R218" t="n">
-        <v>6562366</v>
+        <v>6562364</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -26134,12 +26125,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -26148,34 +26139,38 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
-      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>medelrikkärr</t>
+        </is>
       </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104596865</t>
+          <t>https://artportalen.se/Sighting/66416554</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>6223706</v>
+        <v>104596865</v>
       </c>
       <c r="B219" t="n">
-        <v>97985</v>
+        <v>106244</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26183,43 +26178,45 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>224363</v>
+        <v>221144</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>österhaninge, forsla kärr w dalarövägen, Srm</t>
+          <t>V Forsla kärr, Srm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>681632</v>
+        <v>681619</v>
       </c>
       <c r="R219" t="n">
-        <v>6562243</v>
+        <v>6562366</v>
       </c>
       <c r="S219" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -26243,17 +26240,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2012-05-13</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2012-05-13</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>ej R</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -26262,38 +26254,34 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
+      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
-      </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>Igenvuxen mosse</t>
-        </is>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6223706</t>
+          <t>https://artportalen.se/Sighting/104596865</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>6230772</v>
+        <v>6223706</v>
       </c>
       <c r="B220" t="n">
-        <v>97987</v>
+        <v>97985</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26301,16 +26289,16 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>224364</v>
+        <v>224363</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
@@ -26322,7 +26310,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -26361,12 +26349,17 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2010-08-12</t>
+          <t>2012-05-13</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2010-08-12</t>
+          <t>2012-05-13</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>ej R</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -26380,7 +26373,7 @@
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>stigkanter, skogsäng</t>
+          <t>Igenvuxen mosse</t>
         </is>
       </c>
       <c r="AT220" t="inlineStr"/>
@@ -26397,57 +26390,60 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6230772</t>
+          <t>https://artportalen.se/Sighting/6223706</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129785609</v>
+        <v>6230772</v>
       </c>
       <c r="B221" t="n">
-        <v>92640</v>
+        <v>97987</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>757</v>
+        <v>224364</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>V Forsla kärr, Srm</t>
+          <t>österhaninge, forsla kärr w dalarövägen, Srm</t>
         </is>
       </c>
       <c r="Q221" t="n">
         <v>681632</v>
       </c>
       <c r="R221" t="n">
-        <v>6562463</v>
+        <v>6562243</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -26471,12 +26467,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2010-08-12</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2010-08-12</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -26485,34 +26481,38 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>stigkanter, skogsäng</t>
+        </is>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129785609</t>
+          <t>https://artportalen.se/Sighting/6230772</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129785699</v>
+        <v>129785609</v>
       </c>
       <c r="B222" t="n">
-        <v>91909</v>
+        <v>92640</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26520,21 +26520,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1202</v>
+        <v>757</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -26547,10 +26547,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>681605</v>
+        <v>681632</v>
       </c>
       <c r="R222" t="n">
-        <v>6562467</v>
+        <v>6562463</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -26609,38 +26609,38 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129785699</t>
+          <t>https://artportalen.se/Sighting/129785609</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>104494473</v>
+        <v>129785699</v>
       </c>
       <c r="B223" t="n">
-        <v>92564</v>
+        <v>91909</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -26653,10 +26653,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>681629</v>
+        <v>681605</v>
       </c>
       <c r="R223" t="n">
-        <v>6562506</v>
+        <v>6562467</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -26683,17 +26683,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2022-11-05</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2022-11-05</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Ett mindre ex på granlåga.</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -26720,13 +26715,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104494473</t>
+          <t>https://artportalen.se/Sighting/129785699</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>113019813</v>
+        <v>104494473</v>
       </c>
       <c r="B224" t="n">
         <v>92564</v>
@@ -26764,10 +26759,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>681622</v>
+        <v>681629</v>
       </c>
       <c r="R224" t="n">
-        <v>6562497</v>
+        <v>6562506</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26794,12 +26789,17 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2022-11-05</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2022-11-05</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Ett mindre ex på granlåga.</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -26826,16 +26826,16 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113019813</t>
+          <t>https://artportalen.se/Sighting/104494473</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>54917740</v>
+        <v>113019813</v>
       </c>
       <c r="B225" t="n">
-        <v>57947</v>
+        <v>92564</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26843,48 +26843,40 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>102977</v>
+        <v>1339</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Forsla kärr, Srm</t>
+          <t>V Forsla kärr, Srm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>681674</v>
+        <v>681622</v>
       </c>
       <c r="R225" t="n">
-        <v>6562411</v>
+        <v>6562497</v>
       </c>
       <c r="S225" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -26908,22 +26900,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2015-08-23</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2015-08-23</t>
-        </is>
-      </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -26932,61 +26914,68 @@
       <c r="AE225" t="b">
         <v>0</v>
       </c>
+      <c r="AF225" t="inlineStr"/>
       <c r="AG225" t="b">
         <v>0</v>
       </c>
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Anders Tranberg</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Anders Tranberg</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54917740</t>
+          <t>https://artportalen.se/Sighting/113019813</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>131228625</v>
+        <v>54917740</v>
       </c>
       <c r="B226" t="n">
-        <v>58114</v>
+        <v>57947</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -26995,13 +26984,13 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>681619</v>
+        <v>681674</v>
       </c>
       <c r="R226" t="n">
-        <v>6562516</v>
+        <v>6562411</v>
       </c>
       <c r="S226" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -27025,22 +27014,22 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2015-08-23</t>
         </is>
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2015-08-23</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -27051,88 +27040,74 @@
       </c>
       <c r="AG226" t="b">
         <v>0</v>
-      </c>
-      <c r="AH226" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Mats Tapper</t>
+          <t>Anders Tranberg</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Mats Tapper</t>
+          <t>Anders Tranberg</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131228625</t>
+          <t>https://artportalen.se/Sighting/54917740</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>13088534</v>
+        <v>131228625</v>
       </c>
       <c r="B227" t="n">
-        <v>43378</v>
+        <v>58114</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>201075</v>
+        <v>103021</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Forsla kärr  V Skutan  Haninge, Srm</t>
+          <t>Forsla kärr, Srm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>681760</v>
+        <v>681619</v>
       </c>
       <c r="R227" t="n">
-        <v>6562444</v>
+        <v>6562516</v>
       </c>
       <c r="S227" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -27156,17 +27131,22 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2005-07-18</t>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2005-07-18</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>2-4 ex.</t>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -27177,31 +27157,36 @@
       </c>
       <c r="AG227" t="b">
         <v>0</v>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Roger Kaufmann</t>
+          <t>Mats Tapper</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Roger Kaufmann, Ulf Johansson</t>
+          <t>Mats Tapper</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/13088534</t>
+          <t>https://artportalen.se/Sighting/131228625</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>135100717</v>
+        <v>13088534</v>
       </c>
       <c r="B228" t="n">
-        <v>43388</v>
+        <v>43378</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27231,28 +27216,29 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Forsla kärr, västra, Srm</t>
+          <t>Forsla kärr  V Skutan  Haninge, Srm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>681746</v>
+        <v>681760</v>
       </c>
       <c r="R228" t="n">
-        <v>6562466</v>
+        <v>6562444</v>
       </c>
       <c r="S228" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -27276,12 +27262,17 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2005-07-18</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2005-07-18</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>2-4 ex.</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -27290,34 +27281,33 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Roger Kaufmann</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Roger Kaufmann, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135100717</t>
+          <t>https://artportalen.se/Sighting/13088534</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>13088533</v>
+        <v>135100717</v>
       </c>
       <c r="B229" t="n">
-        <v>43454</v>
+        <v>43388</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27325,21 +27315,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>201108</v>
+        <v>201075</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Starrgräsfjäril</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Coenonympha tullia</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Müller, 1764)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -27347,29 +27337,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Forsla kärr  V Skutan  Haninge, Srm</t>
+          <t>Forsla kärr, västra, Srm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>681760</v>
+        <v>681746</v>
       </c>
       <c r="R229" t="n">
-        <v>6562444</v>
+        <v>6562466</v>
       </c>
       <c r="S229" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -27393,12 +27382,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2005-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2005-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -27407,30 +27396,31 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
+      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Roger Kaufmann</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Roger Kaufmann, Ulf Johansson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/13088533</t>
+          <t>https://artportalen.se/Sighting/135100717</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>16081212</v>
+        <v>13088533</v>
       </c>
       <c r="B230" t="n">
         <v>43454</v>
@@ -27460,31 +27450,32 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K230" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Forsla kärr, västra, Srm</t>
+          <t>Forsla kärr  V Skutan  Haninge, Srm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>681746</v>
+        <v>681760</v>
       </c>
       <c r="R230" t="n">
-        <v>6562466</v>
+        <v>6562444</v>
       </c>
       <c r="S230" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -27508,22 +27499,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2014-07-09</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2005-07-18</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2014-07-09</t>
-        </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2005-07-18</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -27538,49 +27519,49 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Roger Kaufmann</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Roger Kaufmann, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16081212</t>
+          <t>https://artportalen.se/Sighting/13088533</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>77001461</v>
+        <v>16081212</v>
       </c>
       <c r="B231" t="n">
-        <v>56689</v>
+        <v>43454</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>206046</v>
+        <v>201108</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Starrgräsfjäril</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Coenonympha tullia</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Müller, 1764)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -27588,27 +27569,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Forsla kärr  V Skutan  Haninge, Srm</t>
+          <t>Forsla kärr, västra, Srm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>681760</v>
+        <v>681746</v>
       </c>
       <c r="R231" t="n">
-        <v>6562444</v>
+        <v>6562466</v>
       </c>
       <c r="S231" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -27632,22 +27614,22 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
+          <t>2014-07-09</t>
         </is>
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2019-04-13</t>
+          <t>2014-07-09</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -27662,68 +27644,77 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Roger Kaufmann</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Roger Kaufmann, Marie Teilmann</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77001461</t>
+          <t>https://artportalen.se/Sighting/16081212</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>16081214</v>
+        <v>77001461</v>
       </c>
       <c r="B232" t="n">
-        <v>99026</v>
+        <v>56689</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>219788</v>
+        <v>206046</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Forsla kärr, västra, Srm</t>
+          <t>Forsla kärr  V Skutan  Haninge, Srm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>681746</v>
+        <v>681760</v>
       </c>
       <c r="R232" t="n">
-        <v>6562466</v>
+        <v>6562444</v>
       </c>
       <c r="S232" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -27747,27 +27738,22 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2014-07-09</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2014-07-09</t>
+          <t>2019-04-13</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Spridd</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -27782,24 +27768,24 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Roger Kaufmann</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Roger Kaufmann, Marie Teilmann</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16081214</t>
+          <t>https://artportalen.se/Sighting/77001461</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>66416549</v>
+        <v>16081214</v>
       </c>
       <c r="B233" t="n">
         <v>99026</v>
@@ -27827,24 +27813,23 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren - yta 02, Srm</t>
+          <t>Forsla kärr, västra, Srm</t>
         </is>
       </c>
       <c r="Q233" t="n">
         <v>681746</v>
       </c>
       <c r="R233" t="n">
-        <v>6562506</v>
+        <v>6562466</v>
       </c>
       <c r="S233" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -27868,12 +27853,27 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2014-07-09</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2014-07-09</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Spridd</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -27884,33 +27884,28 @@
       </c>
       <c r="AG233" t="b">
         <v>0</v>
-      </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>medelrikkärr</t>
-        </is>
       </c>
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416549</t>
+          <t>https://artportalen.se/Sighting/16081214</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>66416550</v>
+        <v>66416549</v>
       </c>
       <c r="B234" t="n">
         <v>99026</v>
@@ -27940,19 +27935,19 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren - yta 03, Srm</t>
+          <t>Forsla kärr, södra myren - yta 02, Srm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>681739</v>
+        <v>681746</v>
       </c>
       <c r="R234" t="n">
-        <v>6562473</v>
+        <v>6562506</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -28015,13 +28010,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416550</t>
+          <t>https://artportalen.se/Sighting/66416549</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>66416551</v>
+        <v>66416550</v>
       </c>
       <c r="B235" t="n">
         <v>99026</v>
@@ -28051,19 +28046,19 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren - yta 04, Srm</t>
+          <t>Forsla kärr, södra myren - yta 03, Srm</t>
         </is>
       </c>
       <c r="Q235" t="n">
         <v>681739</v>
       </c>
       <c r="R235" t="n">
-        <v>6562443</v>
+        <v>6562473</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -28126,13 +28121,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416551</t>
+          <t>https://artportalen.se/Sighting/66416550</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>66416561</v>
+        <v>66416551</v>
       </c>
       <c r="B236" t="n">
         <v>99026</v>
@@ -28162,19 +28157,19 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 17, Srm</t>
+          <t>Forsla kärr, södra myren - yta 04, Srm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>681738</v>
+        <v>681739</v>
       </c>
       <c r="R236" t="n">
-        <v>6562411</v>
+        <v>6562443</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -28237,13 +28232,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416561</t>
+          <t>https://artportalen.se/Sighting/66416551</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>66416564</v>
+        <v>66416561</v>
       </c>
       <c r="B237" t="n">
         <v>99026</v>
@@ -28273,19 +28268,19 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, Srm</t>
+          <t>Forsla kärr, södra myren, yta 17, Srm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>681776</v>
+        <v>681738</v>
       </c>
       <c r="R237" t="n">
-        <v>6562450</v>
+        <v>6562411</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -28348,16 +28343,16 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416564</t>
+          <t>https://artportalen.se/Sighting/66416561</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>110110018</v>
+        <v>66416564</v>
       </c>
       <c r="B238" t="n">
-        <v>99022</v>
+        <v>99026</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28365,57 +28360,41 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>220093</v>
+        <v>219788</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr"/>
-      <c r="N238" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>39</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>SW. Forsla Kärr, Srm</t>
+          <t>Forsla kärr, södra myren, Srm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>681692</v>
+        <v>681776</v>
       </c>
       <c r="R238" t="n">
-        <v>6562439</v>
+        <v>6562450</v>
       </c>
       <c r="S238" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -28439,17 +28418,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>Litet ex., i kanten av kärret..</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -28458,34 +28432,38 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
-      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
+      </c>
+      <c r="AI238" t="inlineStr">
+        <is>
+          <t>medelrikkärr</t>
+        </is>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110110018</t>
+          <t>https://artportalen.se/Sighting/66416564</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>135100690</v>
+        <v>110110018</v>
       </c>
       <c r="B239" t="n">
-        <v>108357</v>
+        <v>99022</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28493,41 +28471,57 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Forsla kärr, västra, Srm</t>
+          <t>SW. Forsla Kärr, Srm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>681689</v>
+        <v>681692</v>
       </c>
       <c r="R239" t="n">
-        <v>6562571</v>
+        <v>6562439</v>
       </c>
       <c r="S239" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -28551,17 +28545,17 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>Återfynd. Sparsamt nedanför barrskogssluttning och stor granrotvälta, mot skogskärr. Endast en blommande stjälk</t>
+          <t>Litet ex., i kanten av kärret..</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -28577,27 +28571,27 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135100690</t>
+          <t>https://artportalen.se/Sighting/110110018</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>72566101</v>
+        <v>135100690</v>
       </c>
       <c r="B240" t="n">
-        <v>92333</v>
+        <v>108357</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28605,43 +28599,41 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>4217</v>
+        <v>220102</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Forsla kärr -NW, Srm</t>
+          <t>Forsla kärr, västra, Srm</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>681677</v>
+        <v>681689</v>
       </c>
       <c r="R240" t="n">
-        <v>6562763</v>
+        <v>6562571</v>
       </c>
       <c r="S240" t="n">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -28665,17 +28657,17 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2018-08-04</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2018-08-04</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>På Tallstock, i bäckdråg</t>
+          <t>Återfynd. Sparsamt nedanför barrskogssluttning och stor granrotvälta, mot skogskärr. Endast en blommande stjälk</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -28691,27 +28683,27 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72566101</t>
+          <t>https://artportalen.se/Sighting/135100690</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>123154565</v>
+        <v>72566101</v>
       </c>
       <c r="B241" t="n">
-        <v>58327</v>
+        <v>92333</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28719,37 +28711,43 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>103015</v>
+        <v>4217</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Albyberg, Srm</t>
+          <t>Forsla kärr -NW, Srm</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>681824</v>
+        <v>681677</v>
       </c>
       <c r="R241" t="n">
-        <v>6562064</v>
+        <v>6562763</v>
       </c>
       <c r="S241" t="n">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -28773,12 +28771,17 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2018-08-04</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2018-08-04</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>På Tallstock, i bäckdråg</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -28787,33 +28790,34 @@
       <c r="AE241" t="b">
         <v>0</v>
       </c>
+      <c r="AF241" t="inlineStr"/>
       <c r="AG241" t="b">
         <v>0</v>
       </c>
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Frida Sjöborg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Frida Sjöborg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123154565</t>
+          <t>https://artportalen.se/Sighting/72566101</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>64954637</v>
+        <v>123154565</v>
       </c>
       <c r="B242" t="n">
-        <v>96350</v>
+        <v>58327</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28821,40 +28825,37 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>2813</v>
+        <v>103015</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Forsla kärr, Srm</t>
+          <t>Albyberg, Srm</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>681873</v>
+        <v>681824</v>
       </c>
       <c r="R242" t="n">
-        <v>6562379</v>
+        <v>6562064</v>
       </c>
       <c r="S242" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -28878,12 +28879,12 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2017-04-11</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2017-04-11</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -28898,70 +28899,65 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Frida Sjöborg</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Frida Sjöborg</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64954637</t>
+          <t>https://artportalen.se/Sighting/123154565</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129772291</v>
+        <v>64954637</v>
       </c>
       <c r="B243" t="n">
-        <v>58114</v>
+        <v>96350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>103021</v>
+        <v>2813</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>S Forsla kärr, Srm</t>
+          <t>Forsla kärr, Srm</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>681797</v>
+        <v>681873</v>
       </c>
       <c r="R243" t="n">
-        <v>6562264</v>
+        <v>6562379</v>
       </c>
       <c r="S243" t="n">
         <v>25</v>
@@ -28988,12 +28984,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2017-04-11</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2017-04-11</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -29008,69 +29004,73 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129772291</t>
+          <t>https://artportalen.se/Sighting/64954637</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>126705817</v>
+        <v>129772291</v>
       </c>
       <c r="B244" t="n">
-        <v>58790</v>
+        <v>58114</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>208245</v>
+        <v>103021</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Forsla kärr, V om Dalarövägen, Srm</t>
+          <t>S Forsla kärr, Srm</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>681818</v>
+        <v>681797</v>
       </c>
       <c r="R244" t="n">
-        <v>6562326</v>
+        <v>6562264</v>
       </c>
       <c r="S244" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -29094,12 +29094,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -29114,27 +29114,27 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Peter Mellroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Peter Mellroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126705817</t>
+          <t>https://artportalen.se/Sighting/129772291</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>66416555</v>
+        <v>126705817</v>
       </c>
       <c r="B245" t="n">
-        <v>99026</v>
+        <v>58790</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29142,41 +29142,41 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>219788</v>
+        <v>208245</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, Srm</t>
+          <t>Forsla kärr, V om Dalarövägen, Srm</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>681794</v>
+        <v>681818</v>
       </c>
       <c r="R245" t="n">
-        <v>6562355</v>
+        <v>6562326</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -29200,12 +29200,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -29216,33 +29216,28 @@
       </c>
       <c r="AG245" t="b">
         <v>0</v>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>medelrikkärr</t>
-        </is>
       </c>
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Peter Mellroth</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Peter Mellroth</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416555</t>
+          <t>https://artportalen.se/Sighting/126705817</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>66416556</v>
+        <v>66416555</v>
       </c>
       <c r="B246" t="n">
         <v>99026</v>
@@ -29272,19 +29267,19 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 11, Srm</t>
+          <t>Forsla kärr, södra myren, Srm</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>681817</v>
+        <v>681794</v>
       </c>
       <c r="R246" t="n">
-        <v>6562346</v>
+        <v>6562355</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -29347,13 +29342,13 @@
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416556</t>
+          <t>https://artportalen.se/Sighting/66416555</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>66416559</v>
+        <v>66416556</v>
       </c>
       <c r="B247" t="n">
         <v>99026</v>
@@ -29383,19 +29378,19 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 15, Srm</t>
+          <t>Forsla kärr, södra myren, yta 11, Srm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>681821</v>
+        <v>681817</v>
       </c>
       <c r="R247" t="n">
-        <v>6562400</v>
+        <v>6562346</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -29458,13 +29453,13 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416559</t>
+          <t>https://artportalen.se/Sighting/66416556</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>66729068</v>
+        <v>66416559</v>
       </c>
       <c r="B248" t="n">
         <v>99026</v>
@@ -29494,19 +29489,19 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra slåttermyren, 300 m VNV - V om Högstalund, Srm</t>
+          <t>Forsla kärr, södra myren, yta 15, Srm</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>681828</v>
+        <v>681821</v>
       </c>
       <c r="R248" t="n">
-        <v>6562373</v>
+        <v>6562400</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -29533,17 +29528,12 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>skärblommig</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -29557,7 +29547,7 @@
       </c>
       <c r="AI248" t="inlineStr">
         <is>
-          <t>rikkärr</t>
+          <t>medelrikkärr</t>
         </is>
       </c>
       <c r="AT248" t="inlineStr"/>
@@ -29574,16 +29564,16 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66729068</t>
+          <t>https://artportalen.se/Sighting/66416559</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>66416176</v>
+        <v>66729068</v>
       </c>
       <c r="B249" t="n">
-        <v>99038</v>
+        <v>99026</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29591,34 +29581,38 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>223597</v>
+        <v>219788</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr"/>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 12, Srm</t>
+          <t>Forsla kärr, södra slåttermyren, 300 m VNV - V om Högstalund, Srm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>681853</v>
+        <v>681828</v>
       </c>
       <c r="R249" t="n">
-        <v>6562374</v>
+        <v>6562373</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -29645,12 +29639,17 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-07-14</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-07-14</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>skärblommig</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -29664,7 +29663,7 @@
       </c>
       <c r="AI249" t="inlineStr">
         <is>
-          <t>medelrikkärr, myrkant</t>
+          <t>rikkärr</t>
         </is>
       </c>
       <c r="AT249" t="inlineStr"/>
@@ -29681,13 +29680,13 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416176</t>
+          <t>https://artportalen.se/Sighting/66729068</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>66728625</v>
+        <v>66416176</v>
       </c>
       <c r="B250" t="n">
         <v>99038</v>
@@ -29713,19 +29712,19 @@
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra slåttermyren, 300 m VNV om Högstalund, Srm</t>
+          <t>Forsla kärr, södra myren, yta 12, Srm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>681827</v>
+        <v>681853</v>
       </c>
       <c r="R250" t="n">
-        <v>6562388</v>
+        <v>6562374</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -29752,12 +29751,12 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29771,7 +29770,7 @@
       </c>
       <c r="AI250" t="inlineStr">
         <is>
-          <t>rikkärr</t>
+          <t>medelrikkärr, myrkant</t>
         </is>
       </c>
       <c r="AT250" t="inlineStr"/>
@@ -29788,13 +29787,13 @@
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66728625</t>
+          <t>https://artportalen.se/Sighting/66416176</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>66728626</v>
+        <v>66728625</v>
       </c>
       <c r="B251" t="n">
         <v>99038</v>
@@ -29820,19 +29819,19 @@
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>57</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra slåttermyren, 300 m VNV - V om Högstalund, Srm</t>
+          <t>Forsla kärr, södra slåttermyren, 300 m VNV om Högstalund, Srm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>681828</v>
+        <v>681827</v>
       </c>
       <c r="R251" t="n">
-        <v>6562373</v>
+        <v>6562388</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29895,16 +29894,16 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66728626</t>
+          <t>https://artportalen.se/Sighting/66728625</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>66333157</v>
+        <v>66728626</v>
       </c>
       <c r="B252" t="n">
-        <v>96458</v>
+        <v>99038</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29912,34 +29911,34 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2818</v>
+        <v>223597</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Forsla kärr, 200 m VNV om Högstalund, Srm</t>
+          <t>Forsla kärr, södra slåttermyren, 300 m VNV - V om Högstalund, Srm</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>681788</v>
+        <v>681828</v>
       </c>
       <c r="R252" t="n">
-        <v>6562630</v>
+        <v>6562373</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -29966,12 +29965,12 @@
       </c>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>2017-06-19</t>
+          <t>2017-07-14</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>2017-06-19</t>
+          <t>2017-07-14</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -29985,7 +29984,7 @@
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>ung alsumpskog vid kärr</t>
+          <t>rikkärr</t>
         </is>
       </c>
       <c r="AT252" t="inlineStr"/>
@@ -30002,16 +30001,16 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66333157</t>
+          <t>https://artportalen.se/Sighting/66728626</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>54003</v>
+        <v>66333157</v>
       </c>
       <c r="B253" t="n">
-        <v>56830</v>
+        <v>96458</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30019,37 +30018,37 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>100092</v>
+        <v>2818</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Forsla kärr (box 2), Srm</t>
+          <t>Forsla kärr, 200 m VNV om Högstalund, Srm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>681852</v>
+        <v>681788</v>
       </c>
       <c r="R253" t="n">
-        <v>6562506</v>
+        <v>6562630</v>
       </c>
       <c r="S253" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -30073,17 +30072,12 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2012-08-13</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2012-08-14</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>2 registreringar</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -30094,82 +30088,74 @@
       </c>
       <c r="AG253" t="b">
         <v>0</v>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>ung alsumpskog vid kärr</t>
+        </is>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Eva Rihm</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Eva Rihm</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54003</t>
+          <t>https://artportalen.se/Sighting/66333157</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>78578090</v>
+        <v>54003</v>
       </c>
       <c r="B254" t="n">
-        <v>43378</v>
+        <v>56830</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>201075</v>
+        <v>100092</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Forsla kärr V om Dalarövägen, Srm</t>
+          <t>Forsla kärr (box 2), Srm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>681831</v>
+        <v>681852</v>
       </c>
       <c r="R254" t="n">
-        <v>6562622</v>
+        <v>6562506</v>
       </c>
       <c r="S254" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -30193,12 +30179,17 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2019-06-22</t>
+          <t>2012-08-13</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2019-06-22</t>
+          <t>2012-08-14</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>2 registreringar</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -30207,72 +30198,84 @@
       <c r="AE254" t="b">
         <v>0</v>
       </c>
-      <c r="AF254" t="inlineStr"/>
       <c r="AG254" t="b">
         <v>0</v>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Björn Phragmén</t>
+          <t>Eva Rihm</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Björn Phragmén</t>
+          <t>Eva Rihm</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78578090</t>
+          <t>https://artportalen.se/Sighting/54003</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>54001</v>
+        <v>78578090</v>
       </c>
       <c r="B255" t="n">
-        <v>56823</v>
+        <v>43378</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>205992</v>
+        <v>201075</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Forsla kärr (box 2), Srm</t>
+          <t>Forsla kärr V om Dalarövägen, Srm</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>681852</v>
+        <v>681831</v>
       </c>
       <c r="R255" t="n">
-        <v>6562506</v>
+        <v>6562622</v>
       </c>
       <c r="S255" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -30296,17 +30299,12 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2012-08-13</t>
+          <t>2019-06-22</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2012-08-14</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>4 registreringar</t>
+          <t>2019-06-22</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -30315,55 +30313,56 @@
       <c r="AE255" t="b">
         <v>0</v>
       </c>
+      <c r="AF255" t="inlineStr"/>
       <c r="AG255" t="b">
         <v>0</v>
       </c>
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Eva Rihm</t>
+          <t>Björn Phragmén</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Eva Rihm</t>
+          <t>Björn Phragmén</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54001</t>
+          <t>https://artportalen.se/Sighting/78578090</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>54002</v>
+        <v>54001</v>
       </c>
       <c r="B256" t="n">
-        <v>56816</v>
+        <v>56823</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -30413,7 +30412,7 @@
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>5 registreringar</t>
+          <t>4 registreringar</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -30439,75 +30438,54 @@
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54002</t>
+          <t>https://artportalen.se/Sighting/54001</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>79688746</v>
+        <v>54002</v>
       </c>
       <c r="B257" t="n">
-        <v>58815</v>
+        <v>56816</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>208250</v>
+        <v>205998</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr"/>
-      <c r="N257" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Forsla kärr- SW, Srm</t>
+          <t>Forsla kärr (box 2), Srm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>681811</v>
+        <v>681852</v>
       </c>
       <c r="R257" t="n">
-        <v>6562533</v>
+        <v>6562506</v>
       </c>
       <c r="S257" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -30531,17 +30509,17 @@
       </c>
       <c r="Y257" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
+          <t>2012-08-13</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
+          <t>2012-08-14</t>
         </is>
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>I lövkärr, mellan barrskog- &amp; öppen mosse. Nos, tydligt skarpt tecknad</t>
+          <t>5 registreringar</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -30550,34 +30528,33 @@
       <c r="AE257" t="b">
         <v>0</v>
       </c>
-      <c r="AF257" t="inlineStr"/>
       <c r="AG257" t="b">
         <v>0</v>
       </c>
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Eva Rihm</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Eva Rihm</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79688746</t>
+          <t>https://artportalen.se/Sighting/54002</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>66333240</v>
+        <v>79688746</v>
       </c>
       <c r="B258" t="n">
-        <v>99026</v>
+        <v>58815</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30585,41 +30562,58 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>219788</v>
+        <v>208250</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Forsla kärr, 125 m VSV Högstalund, Srm</t>
+          <t>Forsla kärr- SW, Srm</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>681849</v>
+        <v>681811</v>
       </c>
       <c r="R258" t="n">
-        <v>6562593</v>
+        <v>6562533</v>
       </c>
       <c r="S258" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -30643,12 +30637,17 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2017-06-19</t>
+          <t>2019-08-31</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2017-06-19</t>
+          <t>2019-08-31</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>I lövkärr, mellan barrskog- &amp; öppen mosse. Nos, tydligt skarpt tecknad</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -30657,35 +30656,31 @@
       <c r="AE258" t="b">
         <v>0</v>
       </c>
+      <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="b">
         <v>0</v>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>övergångsrikkärr</t>
-        </is>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66333240</t>
+          <t>https://artportalen.se/Sighting/79688746</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>66416548</v>
+        <v>66333240</v>
       </c>
       <c r="B259" t="n">
         <v>99026</v>
@@ -30715,19 +30710,19 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren - yta 01, Srm</t>
+          <t>Forsla kärr, 125 m VSV Högstalund, Srm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>681797</v>
+        <v>681849</v>
       </c>
       <c r="R259" t="n">
-        <v>6562505</v>
+        <v>6562593</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -30754,12 +30749,12 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -30773,7 +30768,7 @@
       </c>
       <c r="AI259" t="inlineStr">
         <is>
-          <t>medelrikkärr</t>
+          <t>övergångsrikkärr</t>
         </is>
       </c>
       <c r="AT259" t="inlineStr"/>
@@ -30790,13 +30785,13 @@
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416548</t>
+          <t>https://artportalen.se/Sighting/66333240</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>66416557</v>
+        <v>66416548</v>
       </c>
       <c r="B260" t="n">
         <v>99026</v>
@@ -30826,19 +30821,19 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 13, Srm</t>
+          <t>Forsla kärr, södra myren - yta 01, Srm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>681799</v>
+        <v>681797</v>
       </c>
       <c r="R260" t="n">
-        <v>6562470</v>
+        <v>6562505</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30901,13 +30896,13 @@
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416557</t>
+          <t>https://artportalen.se/Sighting/66416548</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>66416558</v>
+        <v>66416557</v>
       </c>
       <c r="B261" t="n">
         <v>99026</v>
@@ -30937,19 +30932,19 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>72</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 14, Srm</t>
+          <t>Forsla kärr, södra myren, yta 13, Srm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>681821</v>
+        <v>681799</v>
       </c>
       <c r="R261" t="n">
-        <v>6562436</v>
+        <v>6562470</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -31012,13 +31007,13 @@
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416558</t>
+          <t>https://artportalen.se/Sighting/66416557</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>66416560</v>
+        <v>66416558</v>
       </c>
       <c r="B262" t="n">
         <v>99026</v>
@@ -31048,19 +31043,19 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 16, Srm</t>
+          <t>Forsla kärr, södra myren, yta 14, Srm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>681782</v>
+        <v>681821</v>
       </c>
       <c r="R262" t="n">
-        <v>6562428</v>
+        <v>6562436</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -31123,13 +31118,13 @@
       <c r="AY262" t="inlineStr"/>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416560</t>
+          <t>https://artportalen.se/Sighting/66416558</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>66416563</v>
+        <v>66416560</v>
       </c>
       <c r="B263" t="n">
         <v>99026</v>
@@ -31159,19 +31154,19 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, Srm</t>
+          <t>Forsla kärr, södra myren, yta 16, Srm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>681784</v>
+        <v>681782</v>
       </c>
       <c r="R263" t="n">
-        <v>6562441</v>
+        <v>6562428</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -31234,13 +31229,13 @@
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416563</t>
+          <t>https://artportalen.se/Sighting/66416560</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>117799414</v>
+        <v>66416563</v>
       </c>
       <c r="B264" t="n">
         <v>99026</v>
@@ -31270,38 +31265,22 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L264" t="inlineStr"/>
-      <c r="N264" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Forsla kärr- SW, Srm</t>
+          <t>Forsla kärr, södra myren, Srm</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>681811</v>
+        <v>681784</v>
       </c>
       <c r="R264" t="n">
-        <v>6562533</v>
+        <v>6562441</v>
       </c>
       <c r="S264" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -31325,17 +31304,12 @@
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>Öppet mossekärr; Så mänga, som kunde ses, med fältkikare.</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -31344,34 +31318,38 @@
       <c r="AE264" t="b">
         <v>0</v>
       </c>
-      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>medelrikkärr</t>
+        </is>
       </c>
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117799414</t>
+          <t>https://artportalen.se/Sighting/66416563</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>79687073</v>
+        <v>117799414</v>
       </c>
       <c r="B265" t="n">
-        <v>97987</v>
+        <v>99026</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31379,28 +31357,36 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>224364</v>
+        <v>219788</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="inlineStr"/>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L265" t="inlineStr"/>
@@ -31445,17 +31431,17 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AC265" t="inlineStr">
         <is>
-          <t>På Hällmark, mossskikt ! ( Säker, för igenväxning..Fertil )</t>
+          <t>Öppet mossekärr; Så mänga, som kunde ses, med fältkikare.</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -31482,54 +31468,66 @@
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79687073</t>
+          <t>https://artportalen.se/Sighting/117799414</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>66686508</v>
+        <v>79687073</v>
       </c>
       <c r="B266" t="n">
-        <v>103403</v>
+        <v>97987</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>223246</v>
+        <v>224364</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Huds.</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr"/>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Forsla kärr, 180 m NV om Högstalund vid lv, Srm</t>
+          <t>Forsla kärr- SW, Srm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>681846</v>
+        <v>681811</v>
       </c>
       <c r="R266" t="n">
-        <v>6562742</v>
+        <v>6562533</v>
       </c>
       <c r="S266" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -31553,12 +31551,17 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2017-07-12</t>
+          <t>2019-08-31</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2017-07-12</t>
+          <t>2019-08-31</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>På Hällmark, mossskikt ! ( Säker, för igenväxning..Fertil )</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -31567,27 +31570,130 @@
       <c r="AE266" t="b">
         <v>0</v>
       </c>
+      <c r="AF266" t="inlineStr"/>
       <c r="AG266" t="b">
         <v>0</v>
-      </c>
-      <c r="AI266" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79687073</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>66686508</v>
+      </c>
+      <c r="B267" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr"/>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Forsla kärr, 180 m NV om Högstalund vid lv, Srm</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>681846</v>
+      </c>
+      <c r="R267" t="n">
+        <v>6562742</v>
+      </c>
+      <c r="S267" t="n">
+        <v>25</v>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>2017-07-12</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>2017-07-12</t>
+        </is>
+      </c>
+      <c r="AD267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
+      <c r="AT267" t="inlineStr"/>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/66686508</t>
         </is>
@@ -31860,6 +31966,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ267"/>
+  <dimension ref="A1:AZ268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27785,51 +27785,64 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>16081214</v>
+        <v>136493024</v>
       </c>
       <c r="B233" t="n">
-        <v>99026</v>
+        <v>56737</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>219788</v>
+        <v>206046</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>obs av hona med unge/ungar</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Forsla kärr, västra, Srm</t>
+          <t>Forsla kärr, Srm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>681746</v>
+        <v>681695</v>
       </c>
       <c r="R233" t="n">
-        <v>6562466</v>
+        <v>6562505</v>
       </c>
       <c r="S233" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -27853,27 +27866,12 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2014-07-09</t>
-        </is>
-      </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2014-07-09</t>
-        </is>
-      </c>
-      <c r="AB233" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Spridd</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -27888,24 +27886,24 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16081214</t>
+          <t>https://artportalen.se/Sighting/136493024</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>66416549</v>
+        <v>16081214</v>
       </c>
       <c r="B234" t="n">
         <v>99026</v>
@@ -27933,24 +27931,23 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren - yta 02, Srm</t>
+          <t>Forsla kärr, västra, Srm</t>
         </is>
       </c>
       <c r="Q234" t="n">
         <v>681746</v>
       </c>
       <c r="R234" t="n">
-        <v>6562506</v>
+        <v>6562466</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -27974,12 +27971,27 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2014-07-09</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2014-07-09</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>Spridd</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -27990,33 +28002,28 @@
       </c>
       <c r="AG234" t="b">
         <v>0</v>
-      </c>
-      <c r="AI234" t="inlineStr">
-        <is>
-          <t>medelrikkärr</t>
-        </is>
       </c>
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416549</t>
+          <t>https://artportalen.se/Sighting/16081214</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>66416550</v>
+        <v>66416549</v>
       </c>
       <c r="B235" t="n">
         <v>99026</v>
@@ -28046,19 +28053,19 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren - yta 03, Srm</t>
+          <t>Forsla kärr, södra myren - yta 02, Srm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>681739</v>
+        <v>681746</v>
       </c>
       <c r="R235" t="n">
-        <v>6562473</v>
+        <v>6562506</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -28121,13 +28128,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416550</t>
+          <t>https://artportalen.se/Sighting/66416549</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>66416551</v>
+        <v>66416550</v>
       </c>
       <c r="B236" t="n">
         <v>99026</v>
@@ -28157,19 +28164,19 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren - yta 04, Srm</t>
+          <t>Forsla kärr, södra myren - yta 03, Srm</t>
         </is>
       </c>
       <c r="Q236" t="n">
         <v>681739</v>
       </c>
       <c r="R236" t="n">
-        <v>6562443</v>
+        <v>6562473</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -28232,13 +28239,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416551</t>
+          <t>https://artportalen.se/Sighting/66416550</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>66416561</v>
+        <v>66416551</v>
       </c>
       <c r="B237" t="n">
         <v>99026</v>
@@ -28268,19 +28275,19 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 17, Srm</t>
+          <t>Forsla kärr, södra myren - yta 04, Srm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>681738</v>
+        <v>681739</v>
       </c>
       <c r="R237" t="n">
-        <v>6562411</v>
+        <v>6562443</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -28343,13 +28350,13 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416561</t>
+          <t>https://artportalen.se/Sighting/66416551</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>66416564</v>
+        <v>66416561</v>
       </c>
       <c r="B238" t="n">
         <v>99026</v>
@@ -28379,19 +28386,19 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, Srm</t>
+          <t>Forsla kärr, södra myren, yta 17, Srm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>681776</v>
+        <v>681738</v>
       </c>
       <c r="R238" t="n">
-        <v>6562450</v>
+        <v>6562411</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -28454,16 +28461,16 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416564</t>
+          <t>https://artportalen.se/Sighting/66416561</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>110110018</v>
+        <v>66416564</v>
       </c>
       <c r="B239" t="n">
-        <v>99022</v>
+        <v>99026</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28471,57 +28478,41 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>220093</v>
+        <v>219788</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr"/>
-      <c r="N239" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>39</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>SW. Forsla Kärr, Srm</t>
+          <t>Forsla kärr, södra myren, Srm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>681692</v>
+        <v>681776</v>
       </c>
       <c r="R239" t="n">
-        <v>6562439</v>
+        <v>6562450</v>
       </c>
       <c r="S239" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -28545,17 +28536,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>Litet ex., i kanten av kärret..</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -28564,34 +28550,38 @@
       <c r="AE239" t="b">
         <v>0</v>
       </c>
-      <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>medelrikkärr</t>
+        </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110110018</t>
+          <t>https://artportalen.se/Sighting/66416564</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>135100690</v>
+        <v>110110018</v>
       </c>
       <c r="B240" t="n">
-        <v>108357</v>
+        <v>99022</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28599,41 +28589,57 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Forsla kärr, västra, Srm</t>
+          <t>SW. Forsla Kärr, Srm</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>681689</v>
+        <v>681692</v>
       </c>
       <c r="R240" t="n">
-        <v>6562571</v>
+        <v>6562439</v>
       </c>
       <c r="S240" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -28657,17 +28663,17 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>Återfynd. Sparsamt nedanför barrskogssluttning och stor granrotvälta, mot skogskärr. Endast en blommande stjälk</t>
+          <t>Litet ex., i kanten av kärret..</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -28683,27 +28689,27 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135100690</t>
+          <t>https://artportalen.se/Sighting/110110018</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>72566101</v>
+        <v>135100690</v>
       </c>
       <c r="B241" t="n">
-        <v>92333</v>
+        <v>108357</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28711,43 +28717,41 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>4217</v>
+        <v>220102</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Forsla kärr -NW, Srm</t>
+          <t>Forsla kärr, västra, Srm</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>681677</v>
+        <v>681689</v>
       </c>
       <c r="R241" t="n">
-        <v>6562763</v>
+        <v>6562571</v>
       </c>
       <c r="S241" t="n">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -28771,17 +28775,17 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2018-08-04</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2018-08-04</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>På Tallstock, i bäckdråg</t>
+          <t>Återfynd. Sparsamt nedanför barrskogssluttning och stor granrotvälta, mot skogskärr. Endast en blommande stjälk</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -28797,27 +28801,27 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72566101</t>
+          <t>https://artportalen.se/Sighting/135100690</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>123154565</v>
+        <v>72566101</v>
       </c>
       <c r="B242" t="n">
-        <v>58327</v>
+        <v>92333</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28825,37 +28829,43 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>103015</v>
+        <v>4217</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Albyberg, Srm</t>
+          <t>Forsla kärr -NW, Srm</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>681824</v>
+        <v>681677</v>
       </c>
       <c r="R242" t="n">
-        <v>6562064</v>
+        <v>6562763</v>
       </c>
       <c r="S242" t="n">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -28879,12 +28889,17 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2018-08-04</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2018-08-04</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>På Tallstock, i bäckdråg</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -28893,33 +28908,34 @@
       <c r="AE242" t="b">
         <v>0</v>
       </c>
+      <c r="AF242" t="inlineStr"/>
       <c r="AG242" t="b">
         <v>0</v>
       </c>
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Frida Sjöborg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Frida Sjöborg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123154565</t>
+          <t>https://artportalen.se/Sighting/72566101</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>64954637</v>
+        <v>123154565</v>
       </c>
       <c r="B243" t="n">
-        <v>96350</v>
+        <v>58327</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28927,40 +28943,37 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2813</v>
+        <v>103015</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Forsla kärr, Srm</t>
+          <t>Albyberg, Srm</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>681873</v>
+        <v>681824</v>
       </c>
       <c r="R243" t="n">
-        <v>6562379</v>
+        <v>6562064</v>
       </c>
       <c r="S243" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -28984,12 +28997,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2017-04-11</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2017-04-11</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -29004,70 +29017,65 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Frida Sjöborg</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Frida Sjöborg</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64954637</t>
+          <t>https://artportalen.se/Sighting/123154565</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129772291</v>
+        <v>64954637</v>
       </c>
       <c r="B244" t="n">
-        <v>58114</v>
+        <v>96350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>103021</v>
+        <v>2813</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>S Forsla kärr, Srm</t>
+          <t>Forsla kärr, Srm</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>681797</v>
+        <v>681873</v>
       </c>
       <c r="R244" t="n">
-        <v>6562264</v>
+        <v>6562379</v>
       </c>
       <c r="S244" t="n">
         <v>25</v>
@@ -29094,12 +29102,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2017-04-11</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2017-04-11</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -29114,69 +29122,73 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129772291</t>
+          <t>https://artportalen.se/Sighting/64954637</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>126705817</v>
+        <v>129772291</v>
       </c>
       <c r="B245" t="n">
-        <v>58790</v>
+        <v>58114</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>208245</v>
+        <v>103021</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Forsla kärr, V om Dalarövägen, Srm</t>
+          <t>S Forsla kärr, Srm</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>681818</v>
+        <v>681797</v>
       </c>
       <c r="R245" t="n">
-        <v>6562326</v>
+        <v>6562264</v>
       </c>
       <c r="S245" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -29200,12 +29212,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -29220,27 +29232,27 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Peter Mellroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Peter Mellroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126705817</t>
+          <t>https://artportalen.se/Sighting/129772291</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>66416555</v>
+        <v>126705817</v>
       </c>
       <c r="B246" t="n">
-        <v>99026</v>
+        <v>58790</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29248,41 +29260,41 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>219788</v>
+        <v>208245</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, Srm</t>
+          <t>Forsla kärr, V om Dalarövägen, Srm</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>681794</v>
+        <v>681818</v>
       </c>
       <c r="R246" t="n">
-        <v>6562355</v>
+        <v>6562326</v>
       </c>
       <c r="S246" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -29306,12 +29318,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -29322,33 +29334,28 @@
       </c>
       <c r="AG246" t="b">
         <v>0</v>
-      </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>medelrikkärr</t>
-        </is>
       </c>
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Peter Mellroth</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Peter Mellroth</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416555</t>
+          <t>https://artportalen.se/Sighting/126705817</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>66416556</v>
+        <v>66416555</v>
       </c>
       <c r="B247" t="n">
         <v>99026</v>
@@ -29378,19 +29385,19 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 11, Srm</t>
+          <t>Forsla kärr, södra myren, Srm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>681817</v>
+        <v>681794</v>
       </c>
       <c r="R247" t="n">
-        <v>6562346</v>
+        <v>6562355</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -29453,13 +29460,13 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416556</t>
+          <t>https://artportalen.se/Sighting/66416555</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>66416559</v>
+        <v>66416556</v>
       </c>
       <c r="B248" t="n">
         <v>99026</v>
@@ -29489,19 +29496,19 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 15, Srm</t>
+          <t>Forsla kärr, södra myren, yta 11, Srm</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>681821</v>
+        <v>681817</v>
       </c>
       <c r="R248" t="n">
-        <v>6562400</v>
+        <v>6562346</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -29564,13 +29571,13 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416559</t>
+          <t>https://artportalen.se/Sighting/66416556</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>66729068</v>
+        <v>66416559</v>
       </c>
       <c r="B249" t="n">
         <v>99026</v>
@@ -29600,19 +29607,19 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra slåttermyren, 300 m VNV - V om Högstalund, Srm</t>
+          <t>Forsla kärr, södra myren, yta 15, Srm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>681828</v>
+        <v>681821</v>
       </c>
       <c r="R249" t="n">
-        <v>6562373</v>
+        <v>6562400</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -29639,17 +29646,12 @@
       </c>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>skärblommig</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -29663,7 +29665,7 @@
       </c>
       <c r="AI249" t="inlineStr">
         <is>
-          <t>rikkärr</t>
+          <t>medelrikkärr</t>
         </is>
       </c>
       <c r="AT249" t="inlineStr"/>
@@ -29680,16 +29682,16 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66729068</t>
+          <t>https://artportalen.se/Sighting/66416559</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>66416176</v>
+        <v>66729068</v>
       </c>
       <c r="B250" t="n">
-        <v>99038</v>
+        <v>99026</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29697,34 +29699,38 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>223597</v>
+        <v>219788</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr"/>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 12, Srm</t>
+          <t>Forsla kärr, södra slåttermyren, 300 m VNV - V om Högstalund, Srm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>681853</v>
+        <v>681828</v>
       </c>
       <c r="R250" t="n">
-        <v>6562374</v>
+        <v>6562373</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -29751,12 +29757,17 @@
       </c>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-07-14</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-07-14</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>skärblommig</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -29770,7 +29781,7 @@
       </c>
       <c r="AI250" t="inlineStr">
         <is>
-          <t>medelrikkärr, myrkant</t>
+          <t>rikkärr</t>
         </is>
       </c>
       <c r="AT250" t="inlineStr"/>
@@ -29787,13 +29798,13 @@
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416176</t>
+          <t>https://artportalen.se/Sighting/66729068</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>66728625</v>
+        <v>66416176</v>
       </c>
       <c r="B251" t="n">
         <v>99038</v>
@@ -29819,19 +29830,19 @@
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra slåttermyren, 300 m VNV om Högstalund, Srm</t>
+          <t>Forsla kärr, södra myren, yta 12, Srm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>681827</v>
+        <v>681853</v>
       </c>
       <c r="R251" t="n">
-        <v>6562388</v>
+        <v>6562374</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -29858,12 +29869,12 @@
       </c>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -29877,7 +29888,7 @@
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>rikkärr</t>
+          <t>medelrikkärr, myrkant</t>
         </is>
       </c>
       <c r="AT251" t="inlineStr"/>
@@ -29894,13 +29905,13 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66728625</t>
+          <t>https://artportalen.se/Sighting/66416176</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>66728626</v>
+        <v>66728625</v>
       </c>
       <c r="B252" t="n">
         <v>99038</v>
@@ -29926,19 +29937,19 @@
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>57</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra slåttermyren, 300 m VNV - V om Högstalund, Srm</t>
+          <t>Forsla kärr, södra slåttermyren, 300 m VNV om Högstalund, Srm</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>681828</v>
+        <v>681827</v>
       </c>
       <c r="R252" t="n">
-        <v>6562373</v>
+        <v>6562388</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -30001,16 +30012,16 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66728626</t>
+          <t>https://artportalen.se/Sighting/66728625</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>66333157</v>
+        <v>66728626</v>
       </c>
       <c r="B253" t="n">
-        <v>96458</v>
+        <v>99038</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30018,34 +30029,34 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2818</v>
+        <v>223597</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Forsla kärr, 200 m VNV om Högstalund, Srm</t>
+          <t>Forsla kärr, södra slåttermyren, 300 m VNV - V om Högstalund, Srm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>681788</v>
+        <v>681828</v>
       </c>
       <c r="R253" t="n">
-        <v>6562630</v>
+        <v>6562373</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -30072,12 +30083,12 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2017-06-19</t>
+          <t>2017-07-14</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2017-06-19</t>
+          <t>2017-07-14</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -30091,7 +30102,7 @@
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>ung alsumpskog vid kärr</t>
+          <t>rikkärr</t>
         </is>
       </c>
       <c r="AT253" t="inlineStr"/>
@@ -30108,16 +30119,16 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66333157</t>
+          <t>https://artportalen.se/Sighting/66728626</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>54003</v>
+        <v>66333157</v>
       </c>
       <c r="B254" t="n">
-        <v>56830</v>
+        <v>96458</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30125,37 +30136,37 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100092</v>
+        <v>2818</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Forsla kärr (box 2), Srm</t>
+          <t>Forsla kärr, 200 m VNV om Högstalund, Srm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>681852</v>
+        <v>681788</v>
       </c>
       <c r="R254" t="n">
-        <v>6562506</v>
+        <v>6562630</v>
       </c>
       <c r="S254" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -30179,17 +30190,12 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2012-08-13</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2012-08-14</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>2 registreringar</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -30200,82 +30206,74 @@
       </c>
       <c r="AG254" t="b">
         <v>0</v>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>ung alsumpskog vid kärr</t>
+        </is>
       </c>
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Eva Rihm</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Eva Rihm</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54003</t>
+          <t>https://artportalen.se/Sighting/66333157</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>78578090</v>
+        <v>54003</v>
       </c>
       <c r="B255" t="n">
-        <v>43378</v>
+        <v>56830</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>201075</v>
+        <v>100092</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Forsla kärr V om Dalarövägen, Srm</t>
+          <t>Forsla kärr (box 2), Srm</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>681831</v>
+        <v>681852</v>
       </c>
       <c r="R255" t="n">
-        <v>6562622</v>
+        <v>6562506</v>
       </c>
       <c r="S255" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -30299,12 +30297,17 @@
       </c>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>2019-06-22</t>
+          <t>2012-08-13</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>2019-06-22</t>
+          <t>2012-08-14</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>2 registreringar</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -30313,72 +30316,84 @@
       <c r="AE255" t="b">
         <v>0</v>
       </c>
-      <c r="AF255" t="inlineStr"/>
       <c r="AG255" t="b">
         <v>0</v>
       </c>
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Björn Phragmén</t>
+          <t>Eva Rihm</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Björn Phragmén</t>
+          <t>Eva Rihm</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78578090</t>
+          <t>https://artportalen.se/Sighting/54003</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>54001</v>
+        <v>78578090</v>
       </c>
       <c r="B256" t="n">
-        <v>56823</v>
+        <v>43378</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>205992</v>
+        <v>201075</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Forsla kärr (box 2), Srm</t>
+          <t>Forsla kärr V om Dalarövägen, Srm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>681852</v>
+        <v>681831</v>
       </c>
       <c r="R256" t="n">
-        <v>6562506</v>
+        <v>6562622</v>
       </c>
       <c r="S256" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -30402,17 +30417,12 @@
       </c>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>2012-08-13</t>
+          <t>2019-06-22</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>2012-08-14</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>4 registreringar</t>
+          <t>2019-06-22</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -30421,55 +30431,56 @@
       <c r="AE256" t="b">
         <v>0</v>
       </c>
+      <c r="AF256" t="inlineStr"/>
       <c r="AG256" t="b">
         <v>0</v>
       </c>
       <c r="AT256" t="inlineStr"/>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Eva Rihm</t>
+          <t>Björn Phragmén</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Eva Rihm</t>
+          <t>Björn Phragmén</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54001</t>
+          <t>https://artportalen.se/Sighting/78578090</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>54002</v>
+        <v>54001</v>
       </c>
       <c r="B257" t="n">
-        <v>56816</v>
+        <v>56823</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -30519,7 +30530,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>5 registreringar</t>
+          <t>4 registreringar</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -30545,75 +30556,54 @@
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54002</t>
+          <t>https://artportalen.se/Sighting/54001</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>79688746</v>
+        <v>54002</v>
       </c>
       <c r="B258" t="n">
-        <v>58815</v>
+        <v>56816</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>208250</v>
+        <v>205998</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Forsla kärr- SW, Srm</t>
+          <t>Forsla kärr (box 2), Srm</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>681811</v>
+        <v>681852</v>
       </c>
       <c r="R258" t="n">
-        <v>6562533</v>
+        <v>6562506</v>
       </c>
       <c r="S258" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -30637,17 +30627,17 @@
       </c>
       <c r="Y258" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
+          <t>2012-08-13</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
+          <t>2012-08-14</t>
         </is>
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>I lövkärr, mellan barrskog- &amp; öppen mosse. Nos, tydligt skarpt tecknad</t>
+          <t>5 registreringar</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -30656,34 +30646,33 @@
       <c r="AE258" t="b">
         <v>0</v>
       </c>
-      <c r="AF258" t="inlineStr"/>
       <c r="AG258" t="b">
         <v>0</v>
       </c>
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Eva Rihm</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Eva Rihm</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79688746</t>
+          <t>https://artportalen.se/Sighting/54002</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>66333240</v>
+        <v>79688746</v>
       </c>
       <c r="B259" t="n">
-        <v>99026</v>
+        <v>58815</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30691,41 +30680,58 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>219788</v>
+        <v>208250</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Forsla kärr, 125 m VSV Högstalund, Srm</t>
+          <t>Forsla kärr- SW, Srm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>681849</v>
+        <v>681811</v>
       </c>
       <c r="R259" t="n">
-        <v>6562593</v>
+        <v>6562533</v>
       </c>
       <c r="S259" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -30749,12 +30755,17 @@
       </c>
       <c r="Y259" t="inlineStr">
         <is>
-          <t>2017-06-19</t>
+          <t>2019-08-31</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>2017-06-19</t>
+          <t>2019-08-31</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>I lövkärr, mellan barrskog- &amp; öppen mosse. Nos, tydligt skarpt tecknad</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -30763,35 +30774,31 @@
       <c r="AE259" t="b">
         <v>0</v>
       </c>
+      <c r="AF259" t="inlineStr"/>
       <c r="AG259" t="b">
         <v>0</v>
-      </c>
-      <c r="AI259" t="inlineStr">
-        <is>
-          <t>övergångsrikkärr</t>
-        </is>
       </c>
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66333240</t>
+          <t>https://artportalen.se/Sighting/79688746</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>66416548</v>
+        <v>66333240</v>
       </c>
       <c r="B260" t="n">
         <v>99026</v>
@@ -30821,19 +30828,19 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren - yta 01, Srm</t>
+          <t>Forsla kärr, 125 m VSV Högstalund, Srm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>681797</v>
+        <v>681849</v>
       </c>
       <c r="R260" t="n">
-        <v>6562505</v>
+        <v>6562593</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -30860,12 +30867,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-06-19</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -30879,7 +30886,7 @@
       </c>
       <c r="AI260" t="inlineStr">
         <is>
-          <t>medelrikkärr</t>
+          <t>övergångsrikkärr</t>
         </is>
       </c>
       <c r="AT260" t="inlineStr"/>
@@ -30896,13 +30903,13 @@
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416548</t>
+          <t>https://artportalen.se/Sighting/66333240</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>66416557</v>
+        <v>66416548</v>
       </c>
       <c r="B261" t="n">
         <v>99026</v>
@@ -30932,19 +30939,19 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 13, Srm</t>
+          <t>Forsla kärr, södra myren - yta 01, Srm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>681799</v>
+        <v>681797</v>
       </c>
       <c r="R261" t="n">
-        <v>6562470</v>
+        <v>6562505</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -31007,13 +31014,13 @@
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416557</t>
+          <t>https://artportalen.se/Sighting/66416548</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>66416558</v>
+        <v>66416557</v>
       </c>
       <c r="B262" t="n">
         <v>99026</v>
@@ -31043,19 +31050,19 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>72</t>
         </is>
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 14, Srm</t>
+          <t>Forsla kärr, södra myren, yta 13, Srm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>681821</v>
+        <v>681799</v>
       </c>
       <c r="R262" t="n">
-        <v>6562436</v>
+        <v>6562470</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -31118,13 +31125,13 @@
       <c r="AY262" t="inlineStr"/>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416558</t>
+          <t>https://artportalen.se/Sighting/66416557</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>66416560</v>
+        <v>66416558</v>
       </c>
       <c r="B263" t="n">
         <v>99026</v>
@@ -31154,19 +31161,19 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, yta 16, Srm</t>
+          <t>Forsla kärr, södra myren, yta 14, Srm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>681782</v>
+        <v>681821</v>
       </c>
       <c r="R263" t="n">
-        <v>6562428</v>
+        <v>6562436</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -31229,13 +31236,13 @@
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416560</t>
+          <t>https://artportalen.se/Sighting/66416558</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>66416563</v>
+        <v>66416560</v>
       </c>
       <c r="B264" t="n">
         <v>99026</v>
@@ -31265,19 +31272,19 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Forsla kärr, södra myren, Srm</t>
+          <t>Forsla kärr, södra myren, yta 16, Srm</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>681784</v>
+        <v>681782</v>
       </c>
       <c r="R264" t="n">
-        <v>6562441</v>
+        <v>6562428</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -31340,13 +31347,13 @@
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66416563</t>
+          <t>https://artportalen.se/Sighting/66416560</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>117799414</v>
+        <v>66416563</v>
       </c>
       <c r="B265" t="n">
         <v>99026</v>
@@ -31376,38 +31383,22 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L265" t="inlineStr"/>
-      <c r="N265" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Forsla kärr- SW, Srm</t>
+          <t>Forsla kärr, södra myren, Srm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>681811</v>
+        <v>681784</v>
       </c>
       <c r="R265" t="n">
-        <v>6562533</v>
+        <v>6562441</v>
       </c>
       <c r="S265" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -31431,17 +31422,12 @@
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>Öppet mossekärr; Så mänga, som kunde ses, med fältkikare.</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -31450,34 +31436,38 @@
       <c r="AE265" t="b">
         <v>0</v>
       </c>
-      <c r="AF265" t="inlineStr"/>
       <c r="AG265" t="b">
         <v>0</v>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>medelrikkärr</t>
+        </is>
       </c>
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117799414</t>
+          <t>https://artportalen.se/Sighting/66416563</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>79687073</v>
+        <v>117799414</v>
       </c>
       <c r="B266" t="n">
-        <v>97987</v>
+        <v>99026</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31485,28 +31475,36 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>224364</v>
+        <v>219788</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L266" t="inlineStr"/>
@@ -31551,17 +31549,17 @@
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AC266" t="inlineStr">
         <is>
-          <t>På Hällmark, mossskikt ! ( Säker, för igenväxning..Fertil )</t>
+          <t>Öppet mossekärr; Så mänga, som kunde ses, med fältkikare.</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -31588,54 +31586,66 @@
       <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79687073</t>
+          <t>https://artportalen.se/Sighting/117799414</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>66686508</v>
+        <v>79687073</v>
       </c>
       <c r="B267" t="n">
-        <v>103403</v>
+        <v>97987</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>223246</v>
+        <v>224364</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Huds.</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr"/>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Forsla kärr, 180 m NV om Högstalund vid lv, Srm</t>
+          <t>Forsla kärr- SW, Srm</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>681846</v>
+        <v>681811</v>
       </c>
       <c r="R267" t="n">
-        <v>6562742</v>
+        <v>6562533</v>
       </c>
       <c r="S267" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -31659,12 +31669,17 @@
       </c>
       <c r="Y267" t="inlineStr">
         <is>
-          <t>2017-07-12</t>
+          <t>2019-08-31</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>2017-07-12</t>
+          <t>2019-08-31</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>På Hällmark, mossskikt ! ( Säker, för igenväxning..Fertil )</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -31673,27 +31688,130 @@
       <c r="AE267" t="b">
         <v>0</v>
       </c>
+      <c r="AF267" t="inlineStr"/>
       <c r="AG267" t="b">
         <v>0</v>
-      </c>
-      <c r="AI267" t="inlineStr">
-        <is>
-          <t>sumpskog</t>
-        </is>
       </c>
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henry Gudmundson</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
       <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79687073</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>66686508</v>
+      </c>
+      <c r="B268" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr"/>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Forsla kärr, 180 m NV om Högstalund vid lv, Srm</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>681846</v>
+      </c>
+      <c r="R268" t="n">
+        <v>6562742</v>
+      </c>
+      <c r="S268" t="n">
+        <v>25</v>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>2017-07-12</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>2017-07-12</t>
+        </is>
+      </c>
+      <c r="AD268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI268" t="inlineStr">
+        <is>
+          <t>sumpskog</t>
+        </is>
+      </c>
+      <c r="AT268" t="inlineStr"/>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/66686508</t>
         </is>
@@ -31967,6 +32085,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -24869,7 +24869,7 @@
         <v>136475971</v>
       </c>
       <c r="B208" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -24869,7 +24869,7 @@
         <v>136475971</v>
       </c>
       <c r="B208" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -24869,7 +24869,7 @@
         <v>136475971</v>
       </c>
       <c r="B208" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -24988,7 +24988,7 @@
         <v>136475971</v>
       </c>
       <c r="B209" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -24988,7 +24988,7 @@
         <v>136475971</v>
       </c>
       <c r="B209" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -24988,7 +24988,7 @@
         <v>136475971</v>
       </c>
       <c r="B209" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -24988,7 +24988,7 @@
         <v>136475971</v>
       </c>
       <c r="B209" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -24988,7 +24988,7 @@
         <v>136475971</v>
       </c>
       <c r="B209" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -6705,7 +6705,7 @@
         <v>136804180</v>
       </c>
       <c r="B51" t="n">
-        <v>58283</v>
+        <v>58296</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -6705,7 +6705,7 @@
         <v>136804180</v>
       </c>
       <c r="B51" t="n">
-        <v>58296</v>
+        <v>58298</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6737,11 +6737,7 @@
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -6705,7 +6705,7 @@
         <v>136804180</v>
       </c>
       <c r="B51" t="n">
-        <v>58298</v>
+        <v>58308</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -6705,7 +6705,7 @@
         <v>136804180</v>
       </c>
       <c r="B51" t="n">
-        <v>58308</v>
+        <v>58309</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -6705,7 +6705,7 @@
         <v>136804180</v>
       </c>
       <c r="B51" t="n">
-        <v>58309</v>
+        <v>58310</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
